--- a/data/agriculture_request_history.xlsx
+++ b/data/agriculture_request_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46303.71153354138</v>
+        <v>46303.71153354167</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -804,6 +804,37 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>FUEL request created.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AR-2026-27-0002</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46312.70840083558</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CREATED</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PESTICIDE request created.</t>
         </is>
       </c>
     </row>
